--- a/shared_store/properties_db.xlsx
+++ b/shared_store/properties_db.xlsx
@@ -475,67 +475,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>550482</v>
+        <v>652538</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Av. Belgrano 1827, Tigre</t>
+          <t>Av. Rivadavia 4561, Moron</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>563</v>
+        <v>757.8</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>2020</v>
+        <v>1974</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>550482_mock.pdf</t>
+          <t>652538_mock.pdf</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>239789</v>
+        <v>302018</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 4267, Tigre</t>
+          <t>Av. Belgrano 807, La Matanza</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1276.4</v>
+        <v>563.6</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>350</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>1993</v>
+        <v>1964</v>
       </c>
       <c r="G3" t="n">
         <v>14</v>
@@ -545,341 +545,341 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>239789_mock.pdf</t>
+          <t>302018_mock.pdf</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>699807</v>
+        <v>948454</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Calle Moreno 2043, Moron</t>
+          <t>Calle Sarmiento 1628, Tigre</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1054.8</v>
+        <v>957</v>
       </c>
       <c r="D4" t="n">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>699807_mock.pdf</t>
+          <t>948454_mock.pdf</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>851040</v>
+        <v>653798</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Av. Corrientes 4978, Vicente Lopez</t>
+          <t>Av. Rivadavia 2351, Moron</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>627.8</v>
+        <v>1178.6</v>
       </c>
       <c r="D5" t="n">
-        <v>162</v>
+        <v>317</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>2019</v>
+        <v>2001</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>851040_mock.pdf</t>
+          <t>653798_mock.pdf</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>41376</v>
+        <v>455390</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Av. Corrientes 2450, Vicente Lopez</t>
+          <t>Av. Belgrano 2448, Quilmes</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1118.7</v>
+        <v>835.4</v>
       </c>
       <c r="D6" t="n">
-        <v>206</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>2015</v>
+        <v>1959</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>41376_mock.pdf</t>
+          <t>455390_mock.pdf</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>549312</v>
+        <v>945063</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Av. Belgrano 4209, San Isidro</t>
+          <t>Calle Mitre 3999, Moron</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1272.6</v>
+        <v>766.8</v>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>207</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="F7" t="n">
-        <v>2013</v>
+        <v>1975</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>549312_mock.pdf</t>
+          <t>945063_mock.pdf</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>713065</v>
+        <v>360881</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Av. Libertador 4547, Lomas de Zamora</t>
+          <t>Calle Moreno 2410, Tigre</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>217</v>
+        <v>637.6</v>
       </c>
       <c r="D8" t="n">
-        <v>94</v>
+        <v>250</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F8" t="n">
-        <v>1969</v>
+        <v>1986</v>
       </c>
       <c r="G8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>713065_mock.pdf</t>
+          <t>360881_mock.pdf</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>923643</v>
+        <v>264401</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Av. Libertador 3660, Vicente Lopez</t>
+          <t>Av. Corrientes 1050, San Isidro</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>127.3</v>
+        <v>966.8</v>
       </c>
       <c r="D9" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>1957</v>
+        <v>2017</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>923643_mock.pdf</t>
+          <t>264401_mock.pdf</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74654</v>
+        <v>253626</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Av. Corrientes 3353, Lomas de Zamora</t>
+          <t>Av. Corrientes 579, San Isidro</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>177.3</v>
+        <v>426.1</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>1981</v>
+        <v>2009</v>
       </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>74654_mock.pdf</t>
+          <t>253626_mock.pdf</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>814659</v>
+        <v>178230</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calle Moreno 4346, San Isidro</t>
+          <t>Av. Libertador 969, Quilmes</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1345.2</v>
+        <v>296.9</v>
       </c>
       <c r="D11" t="n">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>2005</v>
+        <v>1991</v>
       </c>
       <c r="G11" t="n">
         <v>12</v>
@@ -889,427 +889,427 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>814659_mock.pdf</t>
+          <t>178230_mock.pdf</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>267990</v>
+        <v>533864</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Calle Mitre 864, Tigre</t>
+          <t>Calle Sarmiento 3038, Moron</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>487.2</v>
+        <v>384.9</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>330</v>
       </c>
       <c r="E12" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>1983</v>
+        <v>2009</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>267990_mock.pdf</t>
+          <t>533864_mock.pdf</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>371851</v>
+        <v>432930</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Calle Sarmiento 3081, La Matanza</t>
+          <t>Calle Sarmiento 2795, San Isidro</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>521.3</v>
+        <v>905</v>
       </c>
       <c r="D13" t="n">
-        <v>189</v>
+        <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>2004</v>
+        <v>1984</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>371851_mock.pdf</t>
+          <t>432930_mock.pdf</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>768904</v>
+        <v>844599</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Av. Libertador 3663, Moron</t>
+          <t>Av. Belgrano 2822, Moron</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>186.1</v>
+        <v>559.3</v>
       </c>
       <c r="D14" t="n">
-        <v>319</v>
+        <v>211</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>1961</v>
+        <v>2020</v>
       </c>
       <c r="G14" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>768904_mock.pdf</t>
+          <t>844599_mock.pdf</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>982505</v>
+        <v>842699</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 2352, Moron</t>
+          <t>Av. Libertador 1967, Quilmes</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1347.8</v>
+        <v>230.8</v>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>1974</v>
+        <v>1981</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>982505_mock.pdf</t>
+          <t>842699_mock.pdf</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>256587</v>
+        <v>942366</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Av. Libertador 4150, San Miguel</t>
+          <t>Calle Mitre 2273, Quilmes</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1283.5</v>
+        <v>1065.1</v>
       </c>
       <c r="D16" t="n">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>1975</v>
+        <v>2017</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>256587_mock.pdf</t>
+          <t>942366_mock.pdf</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>584445</v>
+        <v>925478</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Av. San Martin 1671, Lomas de Zamora</t>
+          <t>Av. Rivadavia 3506, Moron</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>446.7</v>
+        <v>427.1</v>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>1985</v>
+        <v>2009</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>584445_mock.pdf</t>
+          <t>925478_mock.pdf</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>307022</v>
+        <v>936921</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 2651, Quilmes</t>
+          <t>Av. Corrientes 3337, Tigre</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1323</v>
+        <v>745</v>
       </c>
       <c r="D18" t="n">
-        <v>259</v>
+        <v>177</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>307022_mock.pdf</t>
+          <t>936921_mock.pdf</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>754155</v>
+        <v>780783</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Av. Libertador 1491, Quilmes</t>
+          <t>Calle Moreno 2309, Quilmes</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>152.3</v>
+        <v>1219.5</v>
       </c>
       <c r="D19" t="n">
-        <v>88</v>
+        <v>350</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="F19" t="n">
-        <v>1983</v>
+        <v>2014</v>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>754155_mock.pdf</t>
+          <t>780783_mock.pdf</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>800814</v>
+        <v>917609</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Av. Corrientes 3583, La Matanza</t>
+          <t>Av. San Martin 185, Lomas de Zamora</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1180.9</v>
+        <v>236</v>
       </c>
       <c r="D20" t="n">
-        <v>311</v>
+        <v>151</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>1982</v>
+        <v>1966</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>800814_mock.pdf</t>
+          <t>917609_mock.pdf</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>42251</v>
+        <v>292001</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Av. Libertador 1136, Vicente Lopez</t>
+          <t>Av. Libertador 1672, Vicente Lopez</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1221.4</v>
+        <v>1209.2</v>
       </c>
       <c r="D21" t="n">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>1985</v>
+        <v>1958</v>
       </c>
       <c r="G21" t="n">
         <v>13</v>
@@ -1319,17 +1319,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>42251_mock.pdf</t>
+          <t>292001_mock.pdf</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>automatizacion OCR</t>
+          <t>carga manual (legacy)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>

--- a/shared_store/properties_db.xlsx
+++ b/shared_store/properties_db.xlsx
@@ -474,37 +474,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>652538</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>525982</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 4561, Moron</t>
+          <t>Calle Sarmiento 2714, Vicente Lopez</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>757.8</v>
+        <v>1243.7</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>1974</v>
+        <v>1959</v>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>652538_mock.pdf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>carga manual (legacy)</t>
@@ -512,85 +510,81 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>302018</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>085352</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Av. Belgrano 807, La Matanza</t>
+          <t>Av. Corrientes 4910, Vicente Lopez</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>563.6</v>
+        <v>718.6</v>
       </c>
       <c r="D3" t="n">
-        <v>350</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>16/08/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>211380</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Av. San Martin 3732, Tigre</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>997.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>154</v>
+      </c>
+      <c r="E4" t="n">
+        <v>77</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1991</v>
+      </c>
+      <c r="G4" t="n">
         <v>22</v>
       </c>
-      <c r="F3" t="n">
-        <v>1964</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>302018_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>948454</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Calle Sarmiento 1628, Tigre</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>957</v>
-      </c>
-      <c r="D4" t="n">
-        <v>115</v>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2014</v>
-      </c>
-      <c r="G4" t="n">
-        <v>26</v>
-      </c>
       <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>948454_mock.pdf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>carga manual (legacy)</t>
@@ -598,42 +592,40 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>16/08/2025</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>653798</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>074706</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 2351, Moron</t>
+          <t>Calle Mitre 1445, Lomas de Zamora</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1178.6</v>
+        <v>472.9</v>
       </c>
       <c r="D5" t="n">
-        <v>317</v>
+        <v>85</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>2001</v>
+        <v>1958</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>653798_mock.pdf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>carga manual (legacy)</t>
@@ -641,42 +633,40 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/03/2022</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>455390</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>831395</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Av. Belgrano 2448, Quilmes</t>
+          <t>Calle Mitre 4480, Lomas de Zamora</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>835.4</v>
+        <v>172.6</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>279</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="G6" t="n">
         <v>9</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>455390_mock.pdf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>carga manual (legacy)</t>
@@ -684,386 +674,368 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>02/02/2022</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>945063</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>912915</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calle Mitre 3999, Moron</t>
+          <t>Calle Mitre 3291, La Matanza</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>766.8</v>
+        <v>417.7</v>
       </c>
       <c r="D7" t="n">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>1975</v>
+        <v>1994</v>
       </c>
       <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>24/06/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>831929</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Av. Belgrano 3425, Tigre</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>114</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1984</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>02/11/2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>506718</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Av. San Martin 1543, Moron</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>762.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>155</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01/08/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>135478</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Calle Mitre 2188, Vicente Lopez</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>459.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>47</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1976</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>736462</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Av. San Martin 410, San Miguel</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>875.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>260</v>
+      </c>
+      <c r="E11" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01/05/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>332356</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Av. Rivadavia 3747, Vicente Lopez</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1262.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>49</v>
+      </c>
+      <c r="E12" t="n">
+        <v>72</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1998</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>12/04/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>415591</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Av. Libertador 3462, Lomas de Zamora</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>442.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" t="n">
+        <v>37</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1977</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02/12/2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>518342</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Av. Belgrano 4892, Lomas de Zamora</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1205.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>169</v>
+      </c>
+      <c r="E14" t="n">
+        <v>51</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1992</v>
+      </c>
+      <c r="G14" t="n">
         <v>7</v>
       </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>945063_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>360881</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Calle Moreno 2410, Tigre</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>637.6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>250</v>
-      </c>
-      <c r="E8" t="n">
-        <v>38</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1986</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>360881_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>264401</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Av. Corrientes 1050, San Isidro</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>966.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>122</v>
-      </c>
-      <c r="E9" t="n">
-        <v>81</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2017</v>
-      </c>
-      <c r="G9" t="n">
-        <v>11</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>264401_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>253626</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Av. Corrientes 579, San Isidro</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>426.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>59</v>
-      </c>
-      <c r="E10" t="n">
-        <v>52</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2009</v>
-      </c>
-      <c r="G10" t="n">
-        <v>22</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>253626_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>178230</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Av. Libertador 969, Quilmes</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>296.9</v>
-      </c>
-      <c r="D11" t="n">
-        <v>351</v>
-      </c>
-      <c r="E11" t="n">
-        <v>44</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1991</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>178230_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>533864</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Calle Sarmiento 3038, Moron</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>384.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>330</v>
-      </c>
-      <c r="E12" t="n">
-        <v>43</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2009</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>533864_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>432930</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Calle Sarmiento 2795, San Isidro</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>905</v>
-      </c>
-      <c r="D13" t="n">
-        <v>87</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1984</v>
-      </c>
-      <c r="G13" t="n">
-        <v>23</v>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>432930_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>844599</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Av. Belgrano 2822, Moron</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>559.3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>211</v>
-      </c>
-      <c r="E14" t="n">
-        <v>88</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>25/03/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>265621</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Calle Mitre 1120, San Isidro</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>809.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>174</v>
+      </c>
+      <c r="E15" t="n">
+        <v>83</v>
+      </c>
+      <c r="F15" t="n">
         <v>2020</v>
-      </c>
-      <c r="G14" t="n">
-        <v>26</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>844599_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>842699</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Av. Libertador 1967, Quilmes</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>230.8</v>
-      </c>
-      <c r="D15" t="n">
-        <v>176</v>
-      </c>
-      <c r="E15" t="n">
-        <v>45</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1981</v>
       </c>
       <c r="G15" t="n">
         <v>22</v>
       </c>
       <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>842699_mock.pdf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>carga manual (legacy)</t>
@@ -1071,42 +1043,40 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>17/05/2025</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>942366</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>258164</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Calle Mitre 2273, Quilmes</t>
+          <t>Calle Sarmiento 478, Moron</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1065.1</v>
+        <v>460.9</v>
       </c>
       <c r="D16" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
-        <v>2017</v>
+        <v>1988</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>942366_mock.pdf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>carga manual (legacy)</t>
@@ -1114,171 +1084,163 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>08/05/2022</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>925478</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>255279</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 3506, Moron</t>
+          <t>Calle Moreno 4500, San Isidro</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>427.1</v>
+        <v>367.5</v>
       </c>
       <c r="D17" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
-        <v>2009</v>
+        <v>1990</v>
       </c>
       <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>02/08/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>520985</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Av. Belgrano 4106, San Isidro</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>82</v>
+      </c>
+      <c r="E18" t="n">
+        <v>78</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1961</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>22/01/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>653503</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Calle Moreno 1222, Moron</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>222.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>212</v>
+      </c>
+      <c r="E19" t="n">
+        <v>31</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>carga manual (legacy)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>05/04/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>946611</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Av. Corrientes 4232, Tigre</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>786</v>
+      </c>
+      <c r="D20" t="n">
+        <v>232</v>
+      </c>
+      <c r="E20" t="n">
         <v>18</v>
       </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>925478_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>936921</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Av. Corrientes 3337, Tigre</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>745</v>
-      </c>
-      <c r="D18" t="n">
-        <v>177</v>
-      </c>
-      <c r="E18" t="n">
-        <v>35</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1960</v>
-      </c>
-      <c r="G18" t="n">
-        <v>14</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>936921_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>780783</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Calle Moreno 2309, Quilmes</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1219.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>350</v>
-      </c>
-      <c r="E19" t="n">
-        <v>43</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2014</v>
-      </c>
-      <c r="G19" t="n">
-        <v>19</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>780783_mock.pdf</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>carga manual (legacy)</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>917609</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Av. San Martin 185, Lomas de Zamora</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>236</v>
-      </c>
-      <c r="D20" t="n">
-        <v>151</v>
-      </c>
-      <c r="E20" t="n">
-        <v>28</v>
-      </c>
       <c r="F20" t="n">
-        <v>1966</v>
+        <v>1990</v>
       </c>
       <c r="G20" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>917609_mock.pdf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>carga manual (legacy)</t>
@@ -1286,42 +1248,40 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>292001</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>025428</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Av. Libertador 1672, Vicente Lopez</t>
+          <t>Calle Mitre 180, Tigre</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1209.2</v>
+        <v>812.7</v>
       </c>
       <c r="D21" t="n">
-        <v>323</v>
+        <v>261</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
-        <v>1958</v>
+        <v>1989</v>
       </c>
       <c r="G21" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>292001_mock.pdf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>carga manual (legacy)</t>
@@ -1329,7 +1289,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>30/01/2025</t>
         </is>
       </c>
     </row>
